--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.18756169997764</v>
+        <v>2.955478776246367</v>
       </c>
       <c r="D2" t="n">
-        <v>17.69959738841013</v>
+        <v>2.876184575616647</v>
       </c>
       <c r="E2" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F2" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.90045034222828</v>
+        <v>2.258823180612096</v>
       </c>
       <c r="D3" t="n">
-        <v>13.02623991941086</v>
+        <v>2.116763986904264</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F3" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.14121409674225</v>
+        <v>1.160447290720616</v>
       </c>
       <c r="D4" t="n">
-        <v>5.911068161154703</v>
+        <v>0.9605485761876393</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F4" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.9239484293863</v>
+        <v>4.050141619775274</v>
       </c>
       <c r="D5" t="n">
-        <v>30.67856566243836</v>
+        <v>4.985266920146233</v>
       </c>
       <c r="E5" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F5" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.22046627254326</v>
+        <v>1.985825769288279</v>
       </c>
       <c r="D6" t="n">
-        <v>12.30623659151139</v>
+        <v>1.9997634461206</v>
       </c>
       <c r="E6" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F6" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.58839798575753</v>
+        <v>7.570614672685599</v>
       </c>
       <c r="D7" t="n">
-        <v>50.5748565978768</v>
+        <v>8.21841419715498</v>
       </c>
       <c r="E7" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F7" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.52996408614167</v>
+        <v>2.036119163998021</v>
       </c>
       <c r="D8" t="n">
-        <v>21.50878623436854</v>
+        <v>3.495177763084888</v>
       </c>
       <c r="E8" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F8" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.1017801582011</v>
+        <v>2.616539275707679</v>
       </c>
       <c r="D9" t="n">
-        <v>26.48310142774153</v>
+        <v>4.303503982007999</v>
       </c>
       <c r="E9" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F9" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98581788664681</v>
+        <v>7.310195406580108</v>
       </c>
       <c r="D10" t="n">
-        <v>45.06796600636912</v>
+        <v>7.323544476034982</v>
       </c>
       <c r="E10" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F10" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.370172514404653</v>
+        <v>0.8726530335907562</v>
       </c>
       <c r="D11" t="n">
-        <v>32.77459890468827</v>
+        <v>5.325872322011844</v>
       </c>
       <c r="E11" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F11" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.02874064574156</v>
+        <v>9.592170354933003</v>
       </c>
       <c r="D12" t="n">
-        <v>60.32642712734812</v>
+        <v>9.80304440819407</v>
       </c>
       <c r="E12" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F12" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.33959949974705</v>
+        <v>1.842684918708895</v>
       </c>
       <c r="D13" t="n">
-        <v>44.69988149280924</v>
+        <v>7.263730742581502</v>
       </c>
       <c r="E13" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F13" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05549585884024</v>
+        <v>2.446518077061538</v>
       </c>
       <c r="D14" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E14" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F14" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5813394495091089</v>
+        <v>0.09446766054523019</v>
       </c>
       <c r="D15" t="n">
-        <v>10.12422836565829</v>
+        <v>1.645187109419473</v>
       </c>
       <c r="E15" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F15" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.93781695822198</v>
+        <v>6.164895255711072</v>
       </c>
       <c r="D16" t="n">
-        <v>31.76476034853718</v>
+        <v>5.161773556637292</v>
       </c>
       <c r="E16" t="n">
-        <v>16.70072824204046</v>
+        <v>2.713868339331575</v>
       </c>
       <c r="F16" t="n">
-        <v>16.60171634842936</v>
+        <v>2.697778906619771</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
